--- a/data/Arisdorf/cost/total_demand.xlsx
+++ b/data/Arisdorf/cost/total_demand.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>354165.5278323949</v>
+        <v>354401.3543392278</v>
       </c>
     </row>
   </sheetData>
